--- a/data/Jugadores/Gandalf.xlsx
+++ b/data/Jugadores/Gandalf.xlsx
@@ -366,6 +366,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="14.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -386,7 +389,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -394,7 +397,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
@@ -405,7 +408,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2">
         <v>2</v>
